--- a/data_processed/results_XGB_m2_floorarea_per_capitaincome.xlsx
+++ b/data_processed/results_XGB_m2_floorarea_per_capitaincome.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.9332" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.9334" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2.337010622024536</v>
+        <v>2.307119131088257</v>
       </c>
       <c r="D2" t="n">
-        <v>9.878202438354492</v>
+        <v>9.243518829345703</v>
       </c>
     </row>
     <row r="3">
@@ -467,14 +467,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.35649108886719</v>
+        <v>4.375567436218262</v>
       </c>
       <c r="D3" t="n">
-        <v>43.77537536621094</v>
+        <v>17.53079795837402</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.332207918167114</v>
+        <v>10.28668689727783</v>
       </c>
       <c r="D4" t="n">
-        <v>9.857902526855469</v>
+        <v>41.21381759643555</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.5558021068573</v>
+        <v>2.311825275421143</v>
       </c>
       <c r="D5" t="n">
-        <v>10.80300235748291</v>
+        <v>9.262373924255371</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9217619895935059</v>
+        <v>3.299357891082764</v>
       </c>
       <c r="D6" t="n">
-        <v>3.896153211593628</v>
+        <v>13.21894359588623</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_middleschool</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6907299757003784</v>
+        <v>0.9813513159751892</v>
       </c>
       <c r="D7" t="n">
-        <v>2.919614553451538</v>
+        <v>3.931803703308105</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>distance_depstore</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.464254379272461</v>
+        <v>1.397407293319702</v>
       </c>
       <c r="D8" t="n">
-        <v>18.8697509765625</v>
+        <v>5.598740100860596</v>
       </c>
     </row>
   </sheetData>
